--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CMG HIDRÁULICA NB TORRENT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CMG HIDRÁULICA NB TORRENT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>11.0602</v>
+        <v>17.1465</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6983</v>
+        <v>13.1028</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3618</v>
+        <v>4.043699999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2401</v>
+        <v>7.438499999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8236</v>
+        <v>6.157900000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4166</v>
+        <v>1.2807</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4083</v>
+        <v>10.5035</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7686</v>
+        <v>7.0589</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6398</v>
+        <v>3.4447</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8319</v>
+        <v>-3.065</v>
       </c>
       <c r="N2" t="n">
-        <v>1.055</v>
+        <v>-0.9008999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2232</v>
+        <v>-2.1641</v>
       </c>
       <c r="P2" t="n">
-        <v>2.4007</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2003</v>
+        <v>-11.2947</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6011</v>
+        <v>9.3474</v>
       </c>
       <c r="S2" t="n">
-        <v>5.359299999999999</v>
+        <v>12.6011</v>
       </c>
       <c r="T2" t="n">
-        <v>5.3108</v>
+        <v>11.2237</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0484</v>
+        <v>1.3773</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9460000000000002</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1794999999999999</v>
+        <v>2.6701</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1195</v>
+        <v>-3.6159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1608</v>
+        <v>8.648</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3096</v>
+        <v>3.5573</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8513</v>
+        <v>5.0906</v>
       </c>
       <c r="G3" t="n">
-        <v>6.734</v>
+        <v>-2.5199</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8254</v>
+        <v>-2.5247</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9086</v>
+        <v>0.004800000000000193</v>
       </c>
       <c r="J3" t="n">
-        <v>5.410200000000001</v>
+        <v>0.5414</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4411</v>
+        <v>-0.9105000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9691</v>
+        <v>1.4519</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3238</v>
+        <v>-3.0613</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6157999999999999</v>
+        <v>-1.6143</v>
       </c>
       <c r="O3" t="n">
-        <v>1.9395</v>
+        <v>-1.4471</v>
       </c>
       <c r="P3" t="n">
-        <v>2.8008</v>
+        <v>1.7525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2003</v>
+        <v>-4.479</v>
       </c>
       <c r="R3" t="n">
-        <v>4.0011</v>
+        <v>6.2315</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5946</v>
+        <v>9.297599999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5002</v>
+        <v>5.994400000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0944</v>
+        <v>3.3031</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.7794</v>
+        <v>0.1177</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5999</v>
+        <v>1.5005</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3793</v>
+        <v>-1.3828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>M. ISIDRO PEÑA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3723</v>
+        <v>0.6079</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2422</v>
+        <v>0.6079</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1302</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5808</v>
+        <v>0.6079</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5108</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0917</v>
+        <v>0.6079</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9703999999999999</v>
+        <v>0.6079</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5904</v>
+        <v>0.6079</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5513</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1308</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6821</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0012</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>4.2012</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3734000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4761</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1027</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>4.2181</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.7376</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1246</v>
+        <v>0.3860000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7094</v>
+        <v>-0.7102000000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4153</v>
+        <v>1.0963</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6694</v>
+        <v>0.05109999999999992</v>
       </c>
       <c r="H5" t="n">
-        <v>1.701</v>
+        <v>-0.7077</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9683</v>
+        <v>0.7585999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>5.108499999999999</v>
+        <v>0.008900000000000019</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0594</v>
+        <v>-0.6234</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0491</v>
+        <v>0.6323</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4391</v>
+        <v>0.04220000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3583999999999999</v>
+        <v>-0.08420000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.08079999999999998</v>
+        <v>0.1263</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6002</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2009</v>
+        <v>-1.1684</v>
       </c>
       <c r="R5" t="n">
-        <v>3.8011</v>
+        <v>0.9736</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6847</v>
+        <v>0.2503</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9979</v>
+        <v>0.1699</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6868000000000001</v>
+        <v>0.0805</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5399</v>
+        <v>0.2795</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7997</v>
+        <v>0.2795</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8078</v>
+        <v>0.1871999999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.5657</v>
+        <v>-3.4114</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3735</v>
+        <v>3.5987</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4418</v>
+        <v>-4.8868</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3786</v>
+        <v>-4.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06320000000000003</v>
+        <v>-0.8264999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8517999999999999</v>
+        <v>-1.6112</v>
       </c>
       <c r="K6" t="n">
-        <v>1.445</v>
+        <v>-2.2775</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2969</v>
+        <v>0.6662999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2936</v>
+        <v>-3.2756</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0665</v>
+        <v>-1.7825</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3601</v>
+        <v>-1.493</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4001</v>
+        <v>1.5579</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.2012</v>
+        <v>-7.0106</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6013</v>
+        <v>8.5685</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.4336</v>
+        <v>1.1746</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.9513</v>
+        <v>1.0181</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4823</v>
+        <v>0.1564</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3996</v>
+        <v>2.3416</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4387</v>
+        <v>4.1922</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0392</v>
+        <v>-1.8505</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,67 +952,67 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3606</v>
+        <v>-0.0886</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8143999999999999</v>
+        <v>0.1782</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1751</v>
+        <v>-0.2668</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04880000000000018</v>
+        <v>0.7355</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6954</v>
+        <v>-0.1966</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7443</v>
+        <v>0.9321</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03620000000000001</v>
+        <v>1.3579</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.638</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6018</v>
+        <v>1.3374</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08500000000000002</v>
+        <v>-0.6224</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.05740000000000001</v>
+        <v>-0.2171</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1425</v>
+        <v>-0.4053</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2000999999999999</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.3895</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2521</v>
+        <v>0.4543</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1624</v>
+        <v>0.4882</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08969999999999999</v>
+        <v>-0.034</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5849</v>
+        <v>-1.1636</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0212</v>
+        <v>-2.254</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4363</v>
+        <v>1.0904</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6641000000000001</v>
+        <v>-0.8513999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1963</v>
+        <v>-0.9324</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8604000000000003</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7466</v>
+        <v>-1.8304</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3163</v>
+        <v>-1.2469</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4303</v>
+        <v>-0.5835</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0825</v>
+        <v>0.979</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5126000000000001</v>
+        <v>0.3145</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5699000000000001</v>
+        <v>0.6645</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>0.7789</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2006</v>
+        <v>-1.0911</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5336</v>
+        <v>-0.4236</v>
       </c>
       <c r="U8" t="n">
-        <v>0.333</v>
+        <v>-0.6676</v>
       </c>
       <c r="V8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4204000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>M. ISIDRO PENA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-1.2742</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9903</v>
+        <v>-0.0426</v>
       </c>
       <c r="F9" t="n">
-        <v>2.389</v>
+        <v>-1.2316</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.679</v>
+        <v>-0.1242</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8595</v>
+        <v>-0.2053</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1806</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2122</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.894</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6818000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4667</v>
+        <v>-0.2053</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03460000000000002</v>
+        <v>-0.2053</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5012000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4004</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.2009</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8005</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4781</v>
+        <v>-0.1237</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4228</v>
+        <v>-0.1237</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0551</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8519</v>
+        <v>-2.0768</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8069</v>
+        <v>-3.4041</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.045</v>
+        <v>1.3272</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6067</v>
+        <v>-0.2155999999999998</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7423</v>
+        <v>2.0677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1356</v>
+        <v>-2.2832</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.678</v>
+        <v>4.359900000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.678</v>
+        <v>3.4028</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.9571999999999998</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0713</v>
+        <v>-4.575600000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0643</v>
+        <v>-1.3353</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1356</v>
+        <v>-3.2403</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-10.5158</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>8.373699999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2452</v>
+        <v>5.7583</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1289</v>
+        <v>3.9512</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1163</v>
+        <v>1.8072</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-5.477399999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.1994</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8097</v>
+        <v>-2.597300000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0674</v>
+        <v>-3.1793</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2577</v>
+        <v>0.5818999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1146</v>
+        <v>1.43</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0622</v>
+        <v>2.8816</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0524</v>
+        <v>-1.4518</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2688</v>
+        <v>2.896799999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0328</v>
+        <v>2.9276</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.236</v>
+        <v>-0.03090000000000004</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8459</v>
+        <v>-1.4667</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0295</v>
+        <v>-0.0459</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1835999999999999</v>
+        <v>-1.4209</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8003</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2006</v>
+        <v>-6.0369</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0008</v>
+        <v>5.2579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1551</v>
+        <v>-2.3584</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6227</v>
+        <v>-1.8707</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7778</v>
+        <v>-0.4876000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3401000000000001</v>
+        <v>-0.8898999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7793999999999999</v>
+        <v>1.8316</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.1195</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1058</v>
+        <v>-2.6746</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2113</v>
+        <v>1.0627</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1055</v>
+        <v>-3.7372</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9393</v>
+        <v>4.9781</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5824</v>
+        <v>0.8794000000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5217</v>
+        <v>4.0985</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2146</v>
+        <v>6.6906</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5268</v>
+        <v>3.6898</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3122</v>
+        <v>3.0008</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1539</v>
+        <v>-1.7126</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9443999999999999</v>
+        <v>-2.8104</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2095</v>
+        <v>1.0977</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.8008</v>
+        <v>3.5052</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.2018</v>
+        <v>-4.0895</v>
       </c>
       <c r="R12" t="n">
-        <v>3.401</v>
+        <v>7.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5945</v>
+        <v>-3.552</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2766</v>
+        <v>-1.7663</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3179</v>
+        <v>-1.7856</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9603</v>
+        <v>-7.605700000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.5006999999999999</v>
+        <v>0.2278</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4596</v>
+        <v>-7.8338</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,148 +1420,382 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.203799999999999</v>
+        <v>-6.585599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.4696</v>
+        <v>-8.8293</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2658</v>
+        <v>2.2438</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.9994</v>
+        <v>-4.2359</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.6368</v>
+        <v>-1.0152</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3625</v>
+        <v>-3.2207</v>
       </c>
       <c r="J13" t="n">
-        <v>-6.411</v>
+        <v>-2.1943</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.1428</v>
+        <v>-0.1614</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2681</v>
+        <v>-2.0328</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5884</v>
+        <v>-2.0416</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.494</v>
+        <v>-0.8536</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.09440000000000004</v>
+        <v>-1.1879</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8003</v>
+        <v>0.3895</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2006</v>
+        <v>-5.4526</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0009</v>
+        <v>5.8421</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9354</v>
+        <v>-3.453</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3777</v>
+        <v>-2.9626</v>
       </c>
       <c r="U13" t="n">
-        <v>1.313</v>
+        <v>-0.4904</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.7136999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5196</v>
+        <v>1.78</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4596</v>
+        <v>-1.0663</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>J. MERENCIO MORENO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CMG HIDRÁULICA NB TORRENT</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-9.744</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-9.567</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1770999999999998</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-8.327400000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-2.1214</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-6.2057</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4.3085</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.0992</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-6.4077</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-4.0188</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-4.2207</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2019000000000002</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.2579</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-6.6211</v>
+      </c>
+      <c r="R14" t="n">
+        <v>11.879</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-5.9566</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-4.8673</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-1.0892</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.718</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6.2301</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-6.9481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E. LLACER SIMLAT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CMG HIDRÁULICA NB TORRENT</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-11.4584</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-12.7427</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.2842</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-7.186500000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-6.556</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.6305000000000001</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-3.3779</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-3.5168</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-3.8087</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-3.0392</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.7693999999999999</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1.1685</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.2316</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-1.3261</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2.3691</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-1.7774</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.4043000000000001</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-2.1816</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D. CALERO BAUTISTA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CMG HIDRÁULICA NB TORRENT</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-11.7556</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-7.479</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-4.2765</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-9.0459</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-4.4247</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-4.6212</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-4.2265</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-2.242</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.9845</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-4.8194</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-2.1827</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-2.6366</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.1684</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-4.0895</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.2579</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6088000000000001</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3295000000000001</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2791999999999999</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-4.4868</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.5074000000000001</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-4.9943</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>CMG HIDRÁULICA NB TORRENT</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.7289</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-12.9873</v>
-      </c>
-      <c r="F14" t="n">
-        <v>29.7165</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4.711800000000002</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.0002999999999993008</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4.7119</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.9665999999999997</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.158999999999999</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1.192299999999999</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.745399999999999</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-2.1589</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.904199999999999</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.000999999999999</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-31.0087</v>
-      </c>
-      <c r="R14" t="n">
-        <v>34.0098</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.679</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.7818</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.1032</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.3376</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13.2731</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-7.935700000000001</v>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-22.4431</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-33.1107</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10.6676</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-22.1525</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-10.7575</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-11.3948</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9.4992</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8.220300000000002</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.279099999999999</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-31.6518</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-18.9776</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-12.6742</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6.8154</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-70.10550000000001</v>
+      </c>
+      <c r="R17" t="n">
+        <v>76.92100000000001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12.2841</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8.791699999999997</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.492299999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-19.3903</v>
+      </c>
+      <c r="W17" t="n">
+        <v>18.7036</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-38.094</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CMG HIDRÁULICA NB TORRENT.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_CMG HIDRÁULICA NB TORRENT.xlsx
@@ -565,13 +565,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>17.1465</v>
+        <v>10.1607</v>
       </c>
       <c r="E2" t="n">
-        <v>13.1028</v>
+        <v>6.1355</v>
       </c>
       <c r="F2" t="n">
-        <v>4.043699999999999</v>
+        <v>4.0251</v>
       </c>
       <c r="G2" t="n">
         <v>7.438499999999999</v>
@@ -610,13 +610,13 @@
         <v>9.3474</v>
       </c>
       <c r="S2" t="n">
-        <v>12.6011</v>
+        <v>5.6153</v>
       </c>
       <c r="T2" t="n">
-        <v>11.2237</v>
+        <v>4.2566</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3773</v>
+        <v>1.3588</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9460000000000002</v>
@@ -643,13 +643,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>8.648</v>
+        <v>3.5169</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5573</v>
+        <v>-0.1824000000000003</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0906</v>
+        <v>3.6993</v>
       </c>
       <c r="G3" t="n">
         <v>-2.5199</v>
@@ -688,13 +688,13 @@
         <v>6.2315</v>
       </c>
       <c r="S3" t="n">
-        <v>9.297599999999999</v>
+        <v>4.1666</v>
       </c>
       <c r="T3" t="n">
-        <v>5.994400000000001</v>
+        <v>2.2548</v>
       </c>
       <c r="U3" t="n">
-        <v>3.3031</v>
+        <v>1.9118</v>
       </c>
       <c r="V3" t="n">
         <v>0.1177</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3860000000000001</v>
+        <v>0.4893000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7102000000000002</v>
+        <v>3.0425</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0963</v>
+        <v>-2.5531</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05109999999999992</v>
+        <v>4.9781</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7077</v>
+        <v>0.8794000000000002</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7585999999999999</v>
+        <v>4.0985</v>
       </c>
       <c r="J5" t="n">
-        <v>0.008900000000000019</v>
+        <v>6.6906</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6234</v>
+        <v>3.6898</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6323</v>
+        <v>3.0008</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04220000000000002</v>
+        <v>-1.7126</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08420000000000001</v>
+        <v>-2.8104</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1263</v>
+        <v>1.0977</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1948</v>
+        <v>3.5052</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1684</v>
+        <v>-4.0895</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9736</v>
+        <v>7.5947</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2503</v>
+        <v>-0.3883999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1699</v>
+        <v>0.2133</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0805</v>
+        <v>-0.6014999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2795</v>
+        <v>-7.605700000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2795</v>
+        <v>0.2278</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-7.8338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1871999999999998</v>
+        <v>0.4417</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.4114</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5987</v>
+        <v>1.1519</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.8868</v>
+        <v>0.05109999999999992</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.0601</v>
+        <v>-0.7077</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8264999999999999</v>
+        <v>0.7585999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.6112</v>
+        <v>0.008900000000000019</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2775</v>
+        <v>-0.6234</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6662999999999999</v>
+        <v>0.6323</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2756</v>
+        <v>0.04220000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7825</v>
+        <v>-0.08420000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.493</v>
+        <v>0.1263</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5579</v>
+        <v>-0.1948</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7.0106</v>
+        <v>-1.1684</v>
       </c>
       <c r="R6" t="n">
-        <v>8.5685</v>
+        <v>0.9736</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1746</v>
+        <v>0.3059</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0181</v>
+        <v>0.1698</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1564</v>
+        <v>0.1361</v>
       </c>
       <c r="V6" t="n">
-        <v>2.3416</v>
+        <v>0.2795</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1922</v>
+        <v>0.2795</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0886</v>
+        <v>0.4012999999999995</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1782</v>
+        <v>-3.3395</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2668</v>
+        <v>3.7406</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7355</v>
+        <v>-4.8868</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1966</v>
+        <v>-4.0601</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9321</v>
+        <v>-0.8264999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3579</v>
+        <v>-1.6112</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>-2.2775</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3374</v>
+        <v>0.6662999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6224</v>
+        <v>-3.2756</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2171</v>
+        <v>-1.7825</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4053</v>
+        <v>-1.493</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5579</v>
+        <v>1.5579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9474</v>
+        <v>-7.0106</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3895</v>
+        <v>8.5685</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4543</v>
+        <v>1.3886</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4882</v>
+        <v>1.09</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.034</v>
+        <v>0.2984999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2795</v>
+        <v>2.3416</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2795</v>
+        <v>4.1922</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.8505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ALONSO ARNEDO</t>
+          <t>C. CAMPILLOS ALONSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1636</v>
+        <v>0.2162000000000004</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.254</v>
+        <v>-0.8387</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0904</v>
+        <v>1.055</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8513999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9324</v>
+        <v>2.8816</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08109999999999999</v>
+        <v>-1.4518</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8304</v>
+        <v>2.896799999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.2469</v>
+        <v>2.9276</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5835</v>
+        <v>-0.03090000000000004</v>
       </c>
       <c r="M8" t="n">
-        <v>0.979</v>
+        <v>-1.4667</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3145</v>
+        <v>-0.0459</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6645</v>
+        <v>-1.4209</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7789</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-6.0369</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7789</v>
+        <v>5.2579</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0911</v>
+        <v>0.4552</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4236</v>
+        <v>0.4698</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6676</v>
+        <v>-0.01469999999999991</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.8898999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8316</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ISIDRO PENA</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2742</v>
+        <v>-0.332</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0426</v>
+        <v>-0.1208</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2316</v>
+        <v>-0.2112</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1242</v>
+        <v>0.7355</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2053</v>
+        <v>-0.1966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.9321</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08110000000000001</v>
+        <v>1.3579</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08110000000000001</v>
+        <v>1.3374</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2053</v>
+        <v>-0.6224</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2053</v>
+        <v>-0.2171</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.4053</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1947</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1237</v>
+        <v>0.2109</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1237</v>
+        <v>0.1892</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>M. ALONSO ARNEDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0768</v>
+        <v>-0.475</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4041</v>
+        <v>-1.8931</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3272</v>
+        <v>1.4181</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2155999999999998</v>
+        <v>-0.8513999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0677</v>
+        <v>-0.9324</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2832</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>4.359900000000001</v>
+        <v>-1.8304</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4028</v>
+        <v>-1.2469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9571999999999998</v>
+        <v>-0.5835</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.575600000000001</v>
+        <v>0.979</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3353</v>
+        <v>0.3145</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2403</v>
+        <v>0.6645</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1421</v>
+        <v>0.7789</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.5158</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>8.373699999999999</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>5.7583</v>
+        <v>-0.4027000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9512</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8072</v>
+        <v>-0.3398</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.477399999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.1994</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. CAMPILLOS ALONSO</t>
+          <t>M. ISIDRO PENA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.597300000000001</v>
+        <v>-1.1745</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1793</v>
+        <v>0.0571</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5818999999999999</v>
+        <v>-1.2316</v>
       </c>
       <c r="G11" t="n">
-        <v>1.43</v>
+        <v>-0.1242</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8816</v>
+        <v>-0.2053</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4518</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.896799999999999</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9276</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.03090000000000004</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4667</v>
+        <v>-0.2053</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0459</v>
+        <v>-0.2053</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4209</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.0369</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>5.2579</v>
+        <v>0.1947</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3584</v>
+        <v>-0.024</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8707</v>
+        <v>-0.024</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4876000000000001</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8898999999999999</v>
+        <v>-1.2211</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8316</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7216</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6746</v>
+        <v>-3.1706</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0627</v>
+        <v>-6.5646</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7372</v>
+        <v>3.3938</v>
       </c>
       <c r="G12" t="n">
-        <v>4.9781</v>
+        <v>-4.2359</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8794000000000002</v>
+        <v>-1.0152</v>
       </c>
       <c r="I12" t="n">
-        <v>4.0985</v>
+        <v>-3.2207</v>
       </c>
       <c r="J12" t="n">
-        <v>6.6906</v>
+        <v>-2.1943</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6898</v>
+        <v>-0.1614</v>
       </c>
       <c r="L12" t="n">
-        <v>3.0008</v>
+        <v>-2.0328</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7126</v>
+        <v>-2.0416</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.8104</v>
+        <v>-0.8536</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0977</v>
+        <v>-1.1879</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5052</v>
+        <v>0.3895</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0895</v>
+        <v>-5.4526</v>
       </c>
       <c r="R12" t="n">
-        <v>7.5947</v>
+        <v>5.8421</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.552</v>
+        <v>-0.03810000000000011</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7663</v>
+        <v>-0.6975999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7856</v>
+        <v>0.6596000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.605700000000001</v>
+        <v>0.7136999999999998</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2278</v>
+        <v>1.78</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.8338</v>
+        <v>-1.0663</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.585599999999999</v>
+        <v>-3.5235</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.8293</v>
+        <v>-5.009499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2438</v>
+        <v>1.4861</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.2359</v>
+        <v>-8.327400000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0152</v>
+        <v>-2.1214</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2207</v>
+        <v>-6.2057</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1943</v>
+        <v>-4.3085</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1614</v>
+        <v>2.0992</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.0328</v>
+        <v>-6.4077</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0416</v>
+        <v>-4.0188</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8536</v>
+        <v>-4.2207</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1879</v>
+        <v>0.2019000000000002</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3895</v>
+        <v>5.2579</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.4526</v>
+        <v>-6.6211</v>
       </c>
       <c r="R13" t="n">
-        <v>5.8421</v>
+        <v>11.879</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.453</v>
+        <v>0.2639999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.9626</v>
+        <v>-0.3099999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4904</v>
+        <v>0.5739</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7136999999999998</v>
+        <v>-0.718</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>6.2301</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0663</v>
+        <v>-6.9481</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.744</v>
+        <v>-3.6062</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.567</v>
+        <v>-4.3151</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1770999999999998</v>
+        <v>0.7087999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.327400000000001</v>
+        <v>-0.2155999999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1214</v>
+        <v>2.0677</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.2057</v>
+        <v>-2.2832</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.3085</v>
+        <v>4.359900000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0992</v>
+        <v>3.4028</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.4077</v>
+        <v>0.9571999999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0188</v>
+        <v>-4.575600000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.2207</v>
+        <v>-1.3353</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2019000000000002</v>
+        <v>-3.2403</v>
       </c>
       <c r="P14" t="n">
-        <v>5.2579</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q14" t="n">
-        <v>-6.6211</v>
+        <v>-10.5158</v>
       </c>
       <c r="R14" t="n">
-        <v>11.879</v>
+        <v>8.373699999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.9566</v>
+        <v>4.229</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.8673</v>
+        <v>3.0402</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0892</v>
+        <v>1.1889</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.718</v>
+        <v>-5.477399999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>6.2301</v>
+        <v>-1.1994</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.9481</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.4584</v>
+        <v>-9.0747</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.7427</v>
+        <v>-10.4022</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2842</v>
+        <v>1.3274</v>
       </c>
       <c r="G15" t="n">
         <v>-7.186500000000001</v>
@@ -1624,13 +1624,13 @@
         <v>6.2316</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3261</v>
+        <v>1.0578</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.3691</v>
+        <v>-0.02850000000000008</v>
       </c>
       <c r="U15" t="n">
-        <v>1.043</v>
+        <v>1.0861</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7774</v>
@@ -1657,13 +1657,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.7556</v>
+        <v>-11.4334</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.479</v>
+        <v>-6.795100000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.2765</v>
+        <v>-4.6383</v>
       </c>
       <c r="G16" t="n">
         <v>-9.0459</v>
@@ -1702,13 +1702,13 @@
         <v>5.2579</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6088000000000001</v>
+        <v>0.9310999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3295000000000001</v>
+        <v>1.0135</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2791999999999999</v>
+        <v>-0.08250000000000005</v>
       </c>
       <c r="V16" t="n">
         <v>-4.4868</v>
@@ -1735,13 +1735,13 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>-22.4431</v>
+        <v>-16.9559</v>
       </c>
       <c r="E17" t="n">
-        <v>-33.1107</v>
+        <v>-30.3282</v>
       </c>
       <c r="F17" t="n">
-        <v>10.6676</v>
+        <v>13.3719</v>
       </c>
       <c r="G17" t="n">
         <v>-22.1525</v>
@@ -1756,7 +1756,7 @@
         <v>9.4992</v>
       </c>
       <c r="K17" t="n">
-        <v>8.220300000000002</v>
+        <v>8.220299999999998</v>
       </c>
       <c r="L17" t="n">
         <v>1.279099999999999</v>
@@ -1771,7 +1771,7 @@
         <v>-12.6742</v>
       </c>
       <c r="P17" t="n">
-        <v>6.8154</v>
+        <v>6.815399999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>-70.10550000000001</v>
@@ -1780,13 +1780,13 @@
         <v>76.92100000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>12.2841</v>
+        <v>17.7712</v>
       </c>
       <c r="T17" t="n">
-        <v>8.791699999999997</v>
+        <v>11.5744</v>
       </c>
       <c r="U17" t="n">
-        <v>3.492299999999999</v>
+        <v>6.1969</v>
       </c>
       <c r="V17" t="n">
         <v>-19.3903</v>
